--- a/exports/empleados.xlsx
+++ b/exports/empleados.xlsx
@@ -1,52 +1,279 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Desarrollo\Agilize-Gestion\exports\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEB35FE6-07AF-4518-9742-AC3CDF5048F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-28920" yWindow="-1980" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Lista de Empleados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Lista de Empleados" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="67">
+  <si>
+    <t>Lista de Empleados</t>
+  </si>
+  <si>
+    <t>Legajo</t>
+  </si>
+  <si>
+    <t>Apellido</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>DNI</t>
+  </si>
+  <si>
+    <t>CUIL</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Telefono</t>
+  </si>
+  <si>
+    <t>Departamento</t>
+  </si>
+  <si>
+    <t>Cargo</t>
+  </si>
+  <si>
+    <t>Valor Hora</t>
+  </si>
+  <si>
+    <t>Sueldo Mensual</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>Activo</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>123456789</t>
+  </si>
+  <si>
+    <t>20-12356789-9</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>ALAM</t>
+  </si>
+  <si>
+    <t>12222244</t>
+  </si>
+  <si>
+    <t>20-55558845-1</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>GABRIEL</t>
+  </si>
+  <si>
+    <t>123456554</t>
+  </si>
+  <si>
+    <t>20-12345667-2</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>ISAIAS</t>
+  </si>
+  <si>
+    <t>98765412</t>
+  </si>
+  <si>
+    <t>20-2587784-9</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>333333333</t>
+  </si>
+  <si>
+    <t>33-3333333-3</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
+    <t>11111111</t>
+  </si>
+  <si>
+    <t>20-2215511-2</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>WALTER</t>
+  </si>
+  <si>
+    <t>5487896</t>
+  </si>
+  <si>
+    <t>20-51458441-9</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>EZEQUIEL</t>
+  </si>
+  <si>
+    <t>5468122</t>
+  </si>
+  <si>
+    <t>20-25144845-7</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>ENMANUEL</t>
+  </si>
+  <si>
+    <t>54544445</t>
+  </si>
+  <si>
+    <t>20-2025858-7</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>JUNIOR</t>
+  </si>
+  <si>
+    <t>33255544</t>
+  </si>
+  <si>
+    <t>20-25482554-9</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>LEO</t>
+  </si>
+  <si>
+    <t>6646454</t>
+  </si>
+  <si>
+    <t>48-21554456-2</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00D4AF37"/>
+      <b/>
       <sz val="14"/>
+      <color rgb="FFD4AF37"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002D2D2D"/>
-        <bgColor rgb="002D2D2D"/>
+        <fgColor rgb="FF2D2D2D"/>
+        <bgColor rgb="FF2D2D2D"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,85 +289,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{44446695-767B-4D2B-8EFD-15EB8D558723}"/>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -428,137 +599,383 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Lista de Empleados</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Apellido</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>DNI</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>CUIL</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cargo</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Valor Hora</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Sueldo Mensual</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Loyo</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Jorge</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>95852029</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>20-95852029-9</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>jorgenayati@gmail.com</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Produccion</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Operario</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4618.94</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Activo</t>
-        </is>
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>5000</v>
+      </c>
+      <c r="K5">
+        <v>1169100</v>
+      </c>
+      <c r="L5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6">
+        <v>4500</v>
+      </c>
+      <c r="K6">
+        <v>1052190</v>
+      </c>
+      <c r="L6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7">
+        <v>5000</v>
+      </c>
+      <c r="K7">
+        <v>1169100</v>
+      </c>
+      <c r="L7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9">
+        <v>5000</v>
+      </c>
+      <c r="K9">
+        <v>1169100</v>
+      </c>
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10">
+        <v>4500</v>
+      </c>
+      <c r="K10">
+        <v>1052190</v>
+      </c>
+      <c r="L10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11">
+        <v>5000</v>
+      </c>
+      <c r="K11">
+        <v>1169100</v>
+      </c>
+      <c r="L11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12">
+        <v>4500</v>
+      </c>
+      <c r="K12">
+        <v>1052190</v>
+      </c>
+      <c r="L12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>57</v>
+      </c>
+      <c r="J13">
+        <v>4500</v>
+      </c>
+      <c r="K13">
+        <v>1052190</v>
+      </c>
+      <c r="L13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14">
+        <v>4500</v>
+      </c>
+      <c r="K14">
+        <v>1052190</v>
+      </c>
+      <c r="L14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15">
+        <v>5000</v>
+      </c>
+      <c r="K15">
+        <v>1169100</v>
+      </c>
+      <c r="L15" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
